--- a/db.xlsx
+++ b/db.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N235"/>
+  <dimension ref="A1:N238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="14.08984375" customWidth="1" min="1" max="1"/>
@@ -8367,15 +8367,134 @@
           <t>Exclusions Finalised</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="n">
         <v>2</v>
       </c>
-      <c r="J235" t="inlineStr"/>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Rupaz</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Research and Development</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Ramboda</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>WS3: ALS-to-CPC</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>YYYYYYYY</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>12</v>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>XXXXXXXXXXXXXXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="5" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Nikhil</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Initial Stratification - NFMR</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Elvanbrook and Dalkeith</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>CEAs Delineation</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Rupaz</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Restratification - Regen Check</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Paddington</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Topology / Geometry Check</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="n">
+        <v>4</v>
+      </c>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
